--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.78</v>
+        <v>26.41</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9706</v>
+        <v>0.9433</v>
       </c>
       <c r="H4" s="39" t="n">
         <v>36</v>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.4</v>
+        <v>42.13</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9476</v>
+        <v>0.9351999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>44.9</v>
+        <v>40.4</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2191</v>
+        <v>0.2289</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.8</v>
+        <v>38.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1865</v>
+        <v>1825</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4023</v>
+        <v>0.3722</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>34.5</v>
+        <v>32</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2440</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.677</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>34.2</v>
+        <v>30.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1812</v>
+        <v>-0.1876</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32.3</v>
+        <v>30.9</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.4</v>
+        <v>27.25</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2251</v>
+        <v>-0.2565</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29</v>
+        <v>28.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3843</v>
+        <v>-0.3799</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>35.3</v>
+        <v>38.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0857</v>
+        <v>-0.0762</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.35</v>
+        <v>20.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>202.5</v>
+        <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>145</v>
+        <v>150.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.716</v>
+        <v>0.7811</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.2</v>
+        <v>36.8</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.5</v>
+        <v>49.55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>81.2034</v>
+        <v>82.98309999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.2</v>
+        <v>32.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>36.25</v>
+        <v>35.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.0892</v>
+        <v>-0.103</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4375</v>
+        <v>0.4508</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.75</v>
+        <v>26.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1153</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>30.5</v>
+        <v>29.1</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>108.45</v>
+        <v>107.9</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4846</v>
+        <v>0.4771</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-04 02:48</t>
+          <t>2026-09-08 03:17</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>0.9433</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>0.9351999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.2289</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.3722</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.1876</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.2565</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3799</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.0762</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.7811</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>82.98309999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.103</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.4508</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.1153</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.4771</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17</t>
+          <t>2026-09-09 02:51</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.41</v>
+        <v>26.78</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9433</v>
+        <v>0.9706</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.13</v>
+        <v>42.56</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9351999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>40.2</v>
+        <v>37.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.2</v>
+        <v>49.35</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2289</v>
+        <v>0.2081</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>37.9</v>
+        <v>36.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1825</v>
+        <v>1805</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3722</v>
+        <v>0.3571</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.9</v>
+        <v>31.1</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2470</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.6976</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.2</v>
+        <v>34.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1876</v>
+        <v>-0.1765</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30.7</v>
+        <v>36</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>27.25</v>
+        <v>26.9</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2565</v>
+        <v>-0.266</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.9</v>
+        <v>26.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3799</v>
+        <v>-0.3843</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>58.2</v>
+        <v>57.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0762</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.45</v>
+        <v>20.6</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203.5</v>
+        <v>205</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.7</v>
+        <v>35.7</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>150.5</v>
+        <v>149</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7811</v>
+        <v>0.7633</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.6</v>
+        <v>32.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.55</v>
+        <v>50.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.98309999999999</v>
+        <v>84.76270000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>32.6</v>
+        <v>34.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.103</v>
+        <v>-0.1005</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>76.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4508</v>
+        <v>0.4375</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>34.6</v>
+        <v>32</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.1</v>
+        <v>26.6</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1153</v>
+        <v>-0.0983</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28.9</v>
+        <v>26.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.9</v>
+        <v>109.65</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4771</v>
+        <v>0.501</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>39.1</v>
+        <v>35.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-09 02:51</t>
+          <t>2026-09-10 02:44</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.78</v>
+        <v>26.9</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9706</v>
+        <v>0.9793999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>35.7</v>
+        <v>34.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.56</v>
+        <v>42.53</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.955</v>
+        <v>0.9536</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>49.35</v>
+        <v>48.6</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2081</v>
+        <v>0.1897</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.5</v>
+        <v>33.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3571</v>
+        <v>0.3496</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.1</v>
+        <v>29.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6976</v>
+        <v>0.6942</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1765</v>
+        <v>-0.1638</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>36</v>
+        <v>32.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>26.9</v>
+        <v>27.35</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.266</v>
+        <v>-0.2538</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3843</v>
+        <v>-0.3624</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>35</v>
+        <v>48.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>57.3</v>
+        <v>58.5</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.6</v>
+        <v>20.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>205</v>
+        <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>35.7</v>
+        <v>33.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7633</v>
+        <v>0.7395999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.9</v>
+        <v>30.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>84.76270000000001</v>
+        <v>84.2542</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.8</v>
+        <v>33.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1005</v>
+        <v>-0.103</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.7</v>
+        <v>32.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4375</v>
+        <v>0.4356</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32</v>
+        <v>30.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.6</v>
+        <v>26.25</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.0983</v>
+        <v>-0.1102</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.7</v>
+        <v>25.3</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.501</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-10 02:44</t>
+          <t>2026-09-11 02:35</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.9</v>
+        <v>26.35</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9389</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>34.3</v>
+        <v>27.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.53</v>
+        <v>41.83</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9536</v>
+        <v>0.9215000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>35.6</v>
+        <v>30.7</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1897</v>
+        <v>0.1383</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.6</v>
+        <v>31.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1795</v>
+        <v>1620</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3496</v>
+        <v>0.218</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.8</v>
+        <v>26.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2465</v>
+        <v>2410</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6942</v>
+        <v>0.6564</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1638</v>
+        <v>-0.194</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32.1</v>
+        <v>25.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>27.35</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2538</v>
+        <v>-0.2797</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.3</v>
+        <v>23.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3624</v>
+        <v>-0.3668</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>48.6</v>
+        <v>37.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>58.5</v>
+        <v>59.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0571</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.45</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203.5</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.9</v>
+        <v>32.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>147</v>
+        <v>148.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7395999999999999</v>
+        <v>0.7574</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.3</v>
+        <v>51.7</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>84.2542</v>
+        <v>86.62709999999998</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.8</v>
+        <v>33.1</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.7</v>
+        <v>34.1</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.103</v>
+        <v>-0.1432</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.1</v>
+        <v>27.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4356</v>
+        <v>0.4015</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.6</v>
+        <v>29.1</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.25</v>
+        <v>26.05</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1102</v>
+        <v>-0.1169</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>109.65</v>
+        <v>107.7</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.501</v>
+        <v>0.4743</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>35.1</v>
+        <v>31.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-11 02:35</t>
+          <t>2026-09-15 03:53</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.35</v>
+        <v>26.16</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9389</v>
+        <v>0.9248999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.9</v>
+        <v>29.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.83</v>
+        <v>41.64</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9215000000000001</v>
+        <v>0.9127</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>30.7</v>
+        <v>32.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.5</v>
+        <v>45.75</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1383</v>
+        <v>0.12</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.218</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2410</v>
+        <v>2380</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6564</v>
+        <v>0.6357</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.194</v>
+        <v>-0.1828</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>25.4</v>
+        <v>27.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2797</v>
+        <v>-0.2769</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>23.9</v>
+        <v>25.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3668</v>
+        <v>-0.3624</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>37.4</v>
+        <v>39.2</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0571</v>
+        <v>-0.0587</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>148.5</v>
+        <v>154</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7574</v>
+        <v>0.8225</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>30.8</v>
+        <v>34.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>86.62709999999998</v>
+        <v>87.98309999999999</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.1</v>
+        <v>34.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1432</v>
+        <v>-0.1508</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.9</v>
+        <v>30.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4015</v>
+        <v>0.3939</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.05</v>
+        <v>26.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1169</v>
+        <v>-0.1153</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.7</v>
+        <v>106.9</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4743</v>
+        <v>0.4634</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31.6</v>
+        <v>33.4</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-15 03:53</t>
+          <t>2026-09-16 03:07</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.16</v>
+        <v>25.9</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9248999999999999</v>
+        <v>0.9057999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.64</v>
+        <v>41.37</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9127</v>
+        <v>0.9003</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>32.5</v>
+        <v>31.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>45.75</v>
+        <v>45</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.12</v>
+        <v>0.1016</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>32</v>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.218</v>
+        <v>0.2556</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25.9</v>
+        <v>26.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6357</v>
+        <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.6</v>
+        <v>26.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.4</v>
+        <v>50.3</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1828</v>
+        <v>-0.2003</v>
       </c>
       <c r="H9" s="39" t="n">
         <v>27.2</v>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>26.5</v>
+        <v>25.85</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2769</v>
+        <v>-0.2947</v>
       </c>
       <c r="H10" s="39" t="n">
         <v>25.7</v>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.6</v>
+        <v>14.35</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3624</v>
+        <v>-0.3734</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>39.2</v>
+        <v>36.2</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0587</v>
+        <v>-0.0667</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.3</v>
+        <v>34.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.5</v>
+        <v>32</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8225</v>
+        <v>0.787</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.9</v>
+        <v>32.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>87.98309999999999</v>
+        <v>86.7966</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.9</v>
+        <v>32.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1508</v>
+        <v>-0.1382</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3939</v>
+        <v>0.3845</v>
       </c>
       <c r="H17" s="39" t="n">
         <v>30.9</v>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.1</v>
+        <v>25.95</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1153</v>
+        <v>-0.1203</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.9</v>
+        <v>106.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4634</v>
+        <v>0.4545</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>33.4</v>
+        <v>31.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-16 03:07</t>
+          <t>2026-09-17 02:58</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.9</v>
+        <v>26.09</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9057999999999999</v>
+        <v>0.9198000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.2</v>
+        <v>28.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.37</v>
+        <v>41.61</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9003</v>
+        <v>0.9113</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>31.2</v>
+        <v>35.7</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>45</v>
+        <v>46.55</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1016</v>
+        <v>0.1395</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>32</v>
+        <v>35.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2556</v>
+        <v>0.2857</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6392</v>
+        <v>0.6357</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>26.1</v>
+        <v>27.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.2003</v>
+        <v>-0.1733</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>27.2</v>
+        <v>33.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>25.85</v>
+        <v>26.45</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2947</v>
+        <v>-0.2783</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>25.7</v>
+        <v>31.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.35</v>
+        <v>14.45</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3734</v>
+        <v>-0.369</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36.2</v>
+        <v>38.6</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>58.8</v>
+        <v>60.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0667</v>
+        <v>-0.0444</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.4</v>
+        <v>36.3</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.9</v>
+        <v>19.95</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198</v>
+        <v>198.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.787</v>
+        <v>0.8107</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.6</v>
+        <v>35.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>86.7966</v>
+        <v>85.27120000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1382</v>
+        <v>-0.1457</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>31.2</v>
+        <v>33.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3845</v>
+        <v>0.3807</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.9</v>
+        <v>32.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.95</v>
+        <v>26</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1203</v>
+        <v>-0.1186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.7</v>
+        <v>27.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.25</v>
+        <v>106.9</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4545</v>
+        <v>0.4634</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31.2</v>
+        <v>32.8</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-17 02:58</t>
+          <t>2026-09-18 03:07</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.09</v>
+        <v>26.85</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9198000000000001</v>
+        <v>0.9756999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.7</v>
+        <v>34.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>41.61</v>
+        <v>42.7</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9113</v>
+        <v>0.9614</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.55</v>
+        <v>47.35</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1395</v>
+        <v>0.1591</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>35.5</v>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1710</v>
+        <v>1735</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2857</v>
+        <v>0.3045</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2380</v>
+        <v>2460</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6357</v>
+        <v>0.6907</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.6</v>
+        <v>38.5</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>52</v>
+        <v>53.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1733</v>
+        <v>-0.1463</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>33.6</v>
+        <v>40.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>26.45</v>
+        <v>27.65</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2783</v>
+        <v>-0.2456</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>31.4</v>
+        <v>34.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.45</v>
+        <v>14.6</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.369</v>
+        <v>-0.3624</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>38.6</v>
+        <v>41.1</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>60.2</v>
+        <v>61</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0444</v>
+        <v>-0.0317</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>36.3</v>
+        <v>36.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>19.95</v>
+        <v>20.15</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>198.5</v>
+        <v>200.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>153</v>
+        <v>150.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8107</v>
+        <v>0.7811</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.6</v>
+        <v>36.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.27120000000001</v>
+        <v>85.61020000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.4</v>
+        <v>36.3</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>34</v>
+        <v>34.45</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1457</v>
+        <v>-0.1344</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>33.8</v>
+        <v>30</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>72.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3807</v>
+        <v>0.447</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.5</v>
+        <v>38.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26</v>
+        <v>26.55</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1186</v>
+        <v>-0.1</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.2</v>
+        <v>34.3</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.9</v>
+        <v>109.85</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4634</v>
+        <v>0.5038</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>32.8</v>
+        <v>39</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-18 03:07</t>
+          <t>2026-09-22 04:02</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.85</v>
+        <v>27.23</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9756999999999999</v>
+        <v>1.0037</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.7</v>
+        <v>43.39</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9614</v>
+        <v>0.9931</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>38.1</v>
+        <v>38.4</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.35</v>
+        <v>46.65</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1591</v>
+        <v>0.142</v>
       </c>
       <c r="H6" s="39" t="n">
         <v>35.5</v>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1735</v>
+        <v>1875</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3045</v>
+        <v>0.4097999999999999</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>28.7</v>
+        <v>38.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2460</v>
+        <v>2480</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6907</v>
+        <v>0.7045</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>38.5</v>
+        <v>36.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>53.7</v>
+        <v>59</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1463</v>
+        <v>-0.062</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>40.3</v>
+        <v>43.3</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J9" s="45" t="inlineStr">
+        <is>
+          <t>⚪ 觀察</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>27.65</v>
+        <v>30.4</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2456</v>
+        <v>-0.1705</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>34.9</v>
+        <v>43</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.6</v>
+        <v>14.85</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3624</v>
+        <v>-0.3515</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>41.1</v>
+        <v>47.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>61</v>
+        <v>61.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0317</v>
+        <v>-0.0302</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.15</v>
+        <v>20.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>200.5</v>
+        <v>201.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36</v>
+        <v>33.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>150.5</v>
+        <v>154.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7811</v>
+        <v>0.8284</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.1</v>
+        <v>38.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>85.61020000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>34.45</v>
+        <v>35.5</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1344</v>
+        <v>-0.108</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30</v>
+        <v>32.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>76.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.447</v>
+        <v>0.4186</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>38.7</v>
+        <v>32.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.55</v>
+        <v>26</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1</v>
+        <v>-0.1186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>34.3</v>
+        <v>27.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>109.85</v>
+        <v>111.35</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5038</v>
+        <v>0.5243</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>39</v>
+        <v>40.9</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-22 04:02</t>
+          <t>2026-09-23 03:00</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.23</v>
+        <v>27.45</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0037</v>
+        <v>1.0199</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>34.1</v>
+        <v>37.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.39</v>
+        <v>43.71</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9931</v>
+        <v>1.0078</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.65</v>
+        <v>46.5</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.142</v>
+        <v>0.1383</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>35.5</v>
+        <v>33.6</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4097999999999999</v>
+        <v>0.4286</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>38.3</v>
+        <v>32.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2480</v>
+        <v>2460</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7045</v>
+        <v>0.6907</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>36.9</v>
+        <v>34.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59</v>
+        <v>60.3</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.062</v>
+        <v>-0.0413</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>43.3</v>
+        <v>42.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1705</v>
+        <v>-0.1787</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>43</v>
+        <v>35.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3515</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>47.8</v>
+        <v>38.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0302</v>
+        <v>-0.0349</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>37.7</v>
+        <v>35.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.25</v>
+        <v>20.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>201.5</v>
+        <v>204</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.8</v>
+        <v>36.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.8284</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.61020000000001</v>
+        <v>84.5932</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.7</v>
+        <v>31.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.5</v>
+        <v>34.9</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.108</v>
+        <v>-0.1231</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.9</v>
+        <v>28.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>74.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4186</v>
+        <v>0.4091</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.8</v>
+        <v>30.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1186</v>
+        <v>-0.1288</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.5</v>
+        <v>25.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>111.35</v>
+        <v>111.85</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5243</v>
+        <v>0.5311</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>40.9</v>
+        <v>37.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-23 03:00</t>
+          <t>2026-09-24 03:08</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.45</v>
+        <v>27.6</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0199</v>
+        <v>1.0309</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>37.2</v>
+        <v>31.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.71</v>
+        <v>43.87</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0078</v>
+        <v>1.0152</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>38.2</v>
+        <v>37.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1383</v>
+        <v>0.1652</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.6</v>
+        <v>32</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4286</v>
+        <v>0.4361</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>32.4</v>
+        <v>29.4</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2460</v>
+        <v>2475</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6907</v>
+        <v>0.701</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>34.4</v>
+        <v>33.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>60.3</v>
+        <v>58.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0413</v>
+        <v>-0.0668</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>42.2</v>
+        <v>32</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J9" s="45" t="inlineStr">
-        <is>
-          <t>⚪ 觀察</t>
+      <c r="J9" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.1</v>
+        <v>30.5</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1787</v>
+        <v>-0.1678</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>35.9</v>
+        <v>33.9</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.85</v>
+        <v>15.45</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3515</v>
+        <v>-0.3253</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>38.5</v>
+        <v>47.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>60.8</v>
+        <v>59.6</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0349</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.1</v>
+        <v>30.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36.6</v>
+        <v>33.9</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>154.5</v>
+        <v>150</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8284</v>
+        <v>0.7751</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.9</v>
+        <v>32.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>84.5932</v>
+        <v>83.06780000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.9</v>
+        <v>29.1</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1231</v>
+        <v>-0.1181</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.7</v>
+        <v>26.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>74.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.4091</v>
+        <v>0.3996</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.7</v>
+        <v>25.55</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1288</v>
+        <v>-0.1339</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>111.85</v>
+        <v>112.4</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5311</v>
+        <v>0.5387</v>
       </c>
       <c r="H23" s="39" t="n">
         <v>37.3</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-24 03:08</t>
+          <t>2026-09-29 05:18</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>1.0309</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>31.4</v>
+        <v>32.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>1.0152</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>37.3</v>
+        <v>38.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.1652</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>32</v>
+        <v>33.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.4361</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.701</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>33.6</v>
+        <v>35.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.0668</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32</v>
+        <v>33.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.1678</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>33.9</v>
+        <v>35.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3253</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>47.7</v>
+        <v>48.9</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.05400000000000001</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>30.5</v>
+        <v>31.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>202</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33.9</v>
+        <v>35.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.7751</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.9</v>
+        <v>34.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>83.06780000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.1</v>
+        <v>30.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.1181</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.3</v>
+        <v>27.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.3996</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.8</v>
+        <v>32</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.1339</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.5387</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>37.3</v>
+        <v>38.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-29 05:18</t>
+          <t>2026-09-30 04:04</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0309</v>
+        <v>1.0162</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>32.6</v>
+        <v>31.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.87</v>
+        <v>43.39</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0152</v>
+        <v>0.9931</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>38.5</v>
+        <v>34.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.6</v>
+        <v>47.15</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1652</v>
+        <v>0.1542</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4361</v>
+        <v>0.3797</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>30.6</v>
+        <v>29.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.701</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0668</v>
+        <v>-0.0588</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>33.2</v>
+        <v>31.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1678</v>
+        <v>-0.1733</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>35.1</v>
+        <v>31.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.45</v>
+        <v>14.9</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3253</v>
+        <v>-0.3493</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>48.9</v>
+        <v>36</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.6</v>
+        <v>58.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.073</v>
       </c>
       <c r="H12" s="39" t="n">
         <v>31.7</v>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>35.1</v>
+        <v>32</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>150</v>
+        <v>151.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.1</v>
+        <v>31.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>83.06780000000001</v>
+        <v>82.22030000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.4</v>
+        <v>29.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>35.1</v>
+        <v>33.85</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1181</v>
+        <v>-0.1495</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3996</v>
+        <v>0.3883</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32</v>
+        <v>30.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.55</v>
+        <v>25.5</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1339</v>
+        <v>-0.1356</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>112.4</v>
+        <v>111.3</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5387</v>
+        <v>0.5236</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>38.5</v>
+        <v>35.1</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-09-30 04:04</t>
+          <t>2026-10-01 04:10</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.4</v>
+        <v>27.65</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0162</v>
+        <v>1.0346</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>31.9</v>
+        <v>34.1</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.39</v>
+        <v>43.65</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9931</v>
+        <v>1.0051</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>34.5</v>
+        <v>37.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.15</v>
+        <v>47.45</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1542</v>
+        <v>0.1616</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1835</v>
+        <v>1890</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3797</v>
+        <v>0.4211</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>29.2</v>
+        <v>31.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2475</v>
+        <v>2480</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.701</v>
+        <v>0.7045</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>35.3</v>
+        <v>36.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59.2</v>
+        <v>59.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0588</v>
+        <v>-0.0604</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.3</v>
+        <v>31.45</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1733</v>
+        <v>-0.1419</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>31.4</v>
+        <v>38.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.9</v>
+        <v>15.35</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3493</v>
+        <v>-0.3297</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36</v>
+        <v>39.2</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>58.4</v>
+        <v>59.4</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.073</v>
+        <v>-0.0571</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.1</v>
+        <v>20.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>200</v>
+        <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32</v>
+        <v>36.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>151.5</v>
+        <v>151</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7929</v>
+        <v>0.787</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>31.1</v>
+        <v>32.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.1</v>
+        <v>49.15</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.22030000000001</v>
+        <v>82.3051</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.2</v>
+        <v>29.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.1495</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3883</v>
+        <v>0.3845</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.9</v>
+        <v>31.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1356</v>
+        <v>-0.122</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.7</v>
+        <v>27.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>111.3</v>
+        <v>112.05</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5236</v>
+        <v>0.5339</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>35.1</v>
+        <v>37.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-01 04:10</t>
+          <t>2026-10-02 04:24</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,22 +933,22 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.65</v>
+        <v>28.59</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0346</v>
+        <v>1.1038</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>34.1</v>
+        <v>46.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J4" s="41" t="inlineStr">
-        <is>
-          <t>🟠 出清</t>
+      <c r="J4" s="45" t="inlineStr">
+        <is>
+          <t>⚪ 觀察</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.65</v>
+        <v>45.11</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0051</v>
+        <v>1.0721</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.45</v>
+        <v>47.9</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1616</v>
+        <v>0.1726</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1890</v>
+        <v>2005</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4211</v>
+        <v>0.5075</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>31.3</v>
+        <v>34.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2480</v>
+        <v>2575</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7045</v>
+        <v>0.7698</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>36.9</v>
+        <v>35.5</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59.1</v>
+        <v>59.6</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0604</v>
+        <v>-0.0525</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>32.4</v>
+        <v>33.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.1419</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>38.1</v>
+        <v>32.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.35</v>
+        <v>14.85</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3297</v>
+        <v>-0.3515</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>39.2</v>
+        <v>34.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.4</v>
+        <v>58.7</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0571</v>
+        <v>-0.0683</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.45</v>
+        <v>20.1</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203.5</v>
+        <v>200</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36.6</v>
+        <v>33</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.787</v>
+        <v>0.7988</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.6</v>
+        <v>35.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.15</v>
+        <v>48.55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.3051</v>
+        <v>81.2881</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>33.85</v>
+        <v>33.9</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1495</v>
+        <v>-0.1482</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>73.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3845</v>
+        <v>0.3598</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.7</v>
+        <v>35.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.9</v>
+        <v>25.3</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.122</v>
+        <v>-0.1424</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.9</v>
+        <v>27</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>112.05</v>
+        <v>115.95</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5339</v>
+        <v>0.5872999999999999</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>37.3</v>
+        <v>39.7</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-02 04:24</t>
+          <t>2026-10-06 06:06</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-06 06:06</t>
+          <t>2026-10-07 04:26</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,22 +933,22 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.59</v>
+        <v>28.64</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1038</v>
+        <v>1.1074</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>46.8</v>
+        <v>37.2</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
-        <is>
-          <t>⚪ 觀察</t>
+      <c r="J4" s="41" t="inlineStr">
+        <is>
+          <t>🟠 出清</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>45.11</v>
+        <v>45.29</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0721</v>
+        <v>1.0804</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>40.5</v>
+        <v>37.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1726</v>
+        <v>0.1677</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5075</v>
+        <v>0.5414</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>34.9</v>
+        <v>30.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7698</v>
+        <v>0.7766</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>35.5</v>
+        <v>33.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0525</v>
+        <v>-0.0604</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>33.6</v>
+        <v>30.5</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.45</v>
+        <v>31.55</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1419</v>
+        <v>-0.1392</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>32.6</v>
+        <v>30.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.85</v>
+        <v>14.5</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3515</v>
+        <v>-0.3668</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>34.4</v>
+        <v>33</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>58.7</v>
+        <v>59.2</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0683</v>
+        <v>-0.0603</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32.7</v>
+        <v>32</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>200</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>33</v>
+        <v>31.5</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>152</v>
+        <v>154.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.7988</v>
+        <v>0.8284</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.4</v>
+        <v>36.2</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>48.55</v>
+        <v>49.3</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>81.2881</v>
+        <v>82.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.2</v>
+        <v>29.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1482</v>
+        <v>-0.1533</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3598</v>
+        <v>0.3466</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>35.3</v>
+        <v>31.4</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1424</v>
+        <v>-0.1458</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27</v>
+        <v>25.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>115.95</v>
+        <v>116.5</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5872999999999999</v>
+        <v>0.5948</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>39.7</v>
+        <v>37.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-07 04:26</t>
+          <t>2026-10-08 04:41</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.64</v>
+        <v>28.37</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.1074</v>
+        <v>1.0876</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>37.2</v>
+        <v>32.8</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>45.29</v>
+        <v>44.68</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0804</v>
+        <v>1.0524</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>37.3</v>
+        <v>36.3</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>47.7</v>
+        <v>48.25</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1677</v>
+        <v>0.1812</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.8</v>
+        <v>35</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>2050</v>
+        <v>1900</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.5414</v>
+        <v>0.4286</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>30.3</v>
+        <v>27.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2585</v>
+        <v>2540</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7766</v>
+        <v>0.7456999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>33.1</v>
+        <v>30.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>59.1</v>
+        <v>57.5</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0604</v>
+        <v>-0.0859</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>31.55</v>
+        <v>30.05</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1392</v>
+        <v>-0.1801</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>30.3</v>
+        <v>28.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>14.5</v>
+        <v>15.15</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3668</v>
+        <v>-0.3384</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <v>-0.0603</v>
+        <v>63.6</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>0.0095</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>32</v>
+        <v>45.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J12" s="42" t="inlineStr">
-        <is>
-          <t>🔴 停損</t>
+      <c r="J12" s="45" t="inlineStr">
+        <is>
+          <t>⚪ 觀察</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>31.5</v>
+        <v>36.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>154.5</v>
+        <v>158.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8284</v>
+        <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
         <v>36.2</v>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>82.55930000000001</v>
+        <v>83.7458</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>29.4</v>
+        <v>31.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>33.7</v>
+        <v>32.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1533</v>
+        <v>-0.1784</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3466</v>
+        <v>0.3504</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.4</v>
+        <v>30.5</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1458</v>
+        <v>-0.139</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>25.2</v>
+        <v>27.8</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>116.5</v>
+        <v>114.8</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5948</v>
+        <v>0.5715</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-08 04:41</t>
+          <t>2026-10-13 06:32</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>1.0876</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>32.8</v>
+        <v>33.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>1.0524</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>36.3</v>
+        <v>36.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.1812</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.4286</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.9</v>
+        <v>28.3</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.7456999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.0859</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.1801</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>28.7</v>
+        <v>29.1</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3384</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>0.0095</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36.3</v>
+        <v>36.8</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>83.7458</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>31.9</v>
+        <v>32.3</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.1784</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.3504</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.139</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.5715</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-13 06:32</t>
+          <t>2026-10-14 04:45</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>28.37</v>
+        <v>27.68</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0876</v>
+        <v>1.0368</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>33.3</v>
+        <v>27.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>44.68</v>
+        <v>43.84</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0524</v>
+        <v>1.0138</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.25</v>
+        <v>48.8</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1812</v>
+        <v>0.1946</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>35.5</v>
+        <v>36.2</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1900</v>
+        <v>1775</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.4286</v>
+        <v>0.3346</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>28.3</v>
+        <v>25</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2540</v>
+        <v>2490</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7456999999999999</v>
+        <v>0.7112999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>31.4</v>
+        <v>29.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>57.5</v>
+        <v>55.3</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.0859</v>
+        <v>-0.1208</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>30.2</v>
+        <v>28.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.05</v>
+        <v>29</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1801</v>
+        <v>-0.2087</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.1</v>
+        <v>27.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.15</v>
+        <v>15.6</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3384</v>
+        <v>-0.3188</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>63.6</v>
+        <v>64.5</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.0095</v>
+        <v>0.0238</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>46</v>
+        <v>40.5</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="J12" s="45" t="inlineStr">
-        <is>
-          <t>⚪ 觀察</t>
+      <c r="J12" s="42" t="inlineStr">
+        <is>
+          <t>🔴 停損</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36.8</v>
+        <v>34.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8756999999999999</v>
+        <v>0.8935</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.6</v>
+        <v>36.3</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>83.7458</v>
+        <v>85.27120000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>32.3</v>
+        <v>30.1</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>32.7</v>
+        <v>31.45</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.1784</v>
+        <v>-0.2098</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>28.1</v>
+        <v>26.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3504</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.139</v>
+        <v>-0.1492</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28.2</v>
+        <v>23.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>114.8</v>
+        <v>112.4</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5715</v>
+        <v>0.5387</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-14 04:45</t>
+          <t>2026-10-15 03:32</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.68</v>
+        <v>27.83</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0368</v>
+        <v>1.0478</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.9</v>
+        <v>28.9</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>43.84</v>
+        <v>44.05</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0138</v>
+        <v>1.0234</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>36.5</v>
+        <v>32.2</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.1946</v>
+        <v>0.224</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.2</v>
+        <v>41.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3346</v>
+        <v>0.3421</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.7112999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>29.3</v>
+        <v>28</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>55.3</v>
+        <v>56.2</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1208</v>
+        <v>-0.1065</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.4</v>
+        <v>29.7</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>29</v>
+        <v>29.9</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2087</v>
+        <v>-0.1842</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3188</v>
+        <v>-0.3231</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>46.4</v>
+        <v>41.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.0238</v>
+        <v>0.0317</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.5</v>
+        <v>20.65</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>204</v>
+        <v>205.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>34.1</v>
+        <v>35.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>160</v>
+        <v>160.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8935</v>
+        <v>0.8994</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>36.3</v>
+        <v>38.4</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.27120000000001</v>
+        <v>85.61020000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.1</v>
+        <v>30.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>31.45</v>
+        <v>31.3</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2098</v>
+        <v>-0.2136</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>26.9</v>
+        <v>30.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.3314</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1492</v>
+        <v>-0.1424</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>23.9</v>
+        <v>26.7</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>112.4</v>
+        <v>113</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5387</v>
+        <v>0.5468999999999999</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-15 03:32</t>
+          <t>2026-10-16 03:17</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>27.83</v>
+        <v>26.87</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>1.0478</v>
+        <v>0.9772</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>28.9</v>
+        <v>26.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>44.05</v>
+        <v>42.48</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>1.0234</v>
+        <v>0.9512999999999999</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>32.2</v>
+        <v>28</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.224</v>
+        <v>0.246</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>41.4</v>
+        <v>41.9</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1785</v>
+        <v>1635</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.3421</v>
+        <v>0.2293</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2490</v>
+        <v>2420</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.7112999999999999</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28</v>
+        <v>27.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>56.2</v>
+        <v>55</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1065</v>
+        <v>-0.1256</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>29.7</v>
+        <v>28.5</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="G10" s="43" t="n">
+        <v>-0.2128</v>
+      </c>
+      <c r="H10" s="39" t="n">
         <v>29.9</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>-0.1842</v>
-      </c>
-      <c r="H10" s="39" t="n">
-        <v>28.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.5</v>
+        <v>15.25</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3231</v>
+        <v>-0.3341</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>41.7</v>
+        <v>37.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>65</v>
+        <v>64.7</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.0317</v>
+        <v>0.027</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.65</v>
+        <v>21.05</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>205.5</v>
+        <v>209.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>35.4</v>
+        <v>43.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>160.5</v>
+        <v>161.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8994</v>
+        <v>0.9112</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>38.4</v>
+        <v>38.9</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>51.1</v>
+        <v>53.7</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>85.61020000000001</v>
+        <v>90.01690000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>30.4</v>
+        <v>39.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>31.3</v>
+        <v>30.1</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2136</v>
+        <v>-0.2437</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.3314</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32.3</v>
+        <v>31.7</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1424</v>
+        <v>-0.1288</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.5468999999999999</v>
+        <v>0.4921</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-16 03:17</t>
+          <t>2026-10-20 04:39</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>26.87</v>
+        <v>25.89</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9772</v>
+        <v>0.9051</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>42.48</v>
+        <v>40.06</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.9512999999999999</v>
+        <v>0.8401000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.246</v>
+        <v>0.2485</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>41.9</v>
+        <v>39.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2293</v>
+        <v>0.2331</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.6631999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.1</v>
+        <v>26.1</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1256</v>
+        <v>-0.1415</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.5</v>
+        <v>26.8</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.85</v>
+        <v>28.3</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2128</v>
+        <v>-0.2278</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>29.9</v>
+        <v>26.8</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.3341</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>37.7</v>
+        <v>34.4</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>64.7</v>
+        <v>63.5</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.027</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>39.9</v>
+        <v>35.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>21.05</v>
+        <v>20.55</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>209.5</v>
+        <v>204.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>43.4</v>
+        <v>34.4</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>161.5</v>
+        <v>158.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.9112</v>
+        <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>38.9</v>
+        <v>32.3</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>90.01690000000001</v>
+        <v>90.35590000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>39.8</v>
+        <v>34.9</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>30.1</v>
+        <v>30.15</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2437</v>
+        <v>-0.2425</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30</v>
+        <v>27.8</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3314</v>
+        <v>0.3295</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1288</v>
+        <v>-0.1186</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>26.4</v>
+        <v>35.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>109</v>
+        <v>108.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4921</v>
+        <v>0.4805</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-20 04:39</t>
+          <t>2026-10-21 03:25</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.89</v>
+        <v>25.54</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9051</v>
+        <v>0.8793000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>40.06</v>
+        <v>39.56</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8401000000000001</v>
+        <v>0.8172</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>51</v>
+        <v>49.95</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2485</v>
+        <v>0.2228</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>39.5</v>
+        <v>36.3</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2331</v>
+        <v>0.2068</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>25.9</v>
+        <v>27.6</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6631999999999999</v>
+        <v>0.6529</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>26.1</v>
+        <v>27.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1415</v>
+        <v>-0.1463</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>26.8</v>
+        <v>28.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2278</v>
+        <v>-0.2306</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.25</v>
+        <v>15.2</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3341</v>
+        <v>-0.3362</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>0.007900000000000001</v>
+        <v>62.2</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.55</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>204.5</v>
+        <v>203</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>158.5</v>
+        <v>153.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8756999999999999</v>
+        <v>0.8166</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>90.35590000000001</v>
+        <v>89.16950000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>34.9</v>
+        <v>36.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>30.15</v>
+        <v>30.2</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2425</v>
+        <v>-0.2412</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.8</v>
+        <v>32.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3295</v>
+        <v>0.3277</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1186</v>
+        <v>-0.1271</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>35.9</v>
+        <v>29.9</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>108.15</v>
+        <v>107.25</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4805</v>
+        <v>0.4682</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-21 03:25</t>
+          <t>2026-10-22 03:25</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.54</v>
+        <v>25.85</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8793000000000001</v>
+        <v>0.9020999999999999</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.3</v>
+        <v>23.6</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.56</v>
+        <v>39.98</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8172</v>
+        <v>0.8365</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>29.5</v>
+        <v>24.9</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>49.95</v>
+        <v>49.9</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2228</v>
+        <v>0.2215</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>36.3</v>
+        <v>33.4</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1605</v>
+        <v>1625</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2068</v>
+        <v>0.2218</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.6</v>
+        <v>23.8</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2405</v>
+        <v>2420</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6529</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.7</v>
+        <v>23.7</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>53.7</v>
+        <v>54</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1463</v>
+        <v>-0.1415</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.4</v>
+        <v>24.6</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>28.2</v>
+        <v>29.9</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.2306</v>
+        <v>-0.1842</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>27.3</v>
+        <v>31.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.2</v>
+        <v>15.15</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3362</v>
+        <v>-0.3384</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0127</v>
+        <v>-0.0143</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.4</v>
+        <v>20.35</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203</v>
+        <v>202.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36</v>
+        <v>32.3</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>153.5</v>
+        <v>158.5</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8166</v>
+        <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>31.5</v>
+        <v>28.7</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>89.16950000000001</v>
+        <v>89.8475</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>36.5</v>
+        <v>33.8</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2412</v>
+        <v>-0.2387</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>32.4</v>
+        <v>27.9</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>70.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3277</v>
+        <v>0.3201</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33.6</v>
+        <v>28.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.75</v>
+        <v>26.1</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1271</v>
+        <v>-0.1153</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>29.9</v>
+        <v>28.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>107.25</v>
+        <v>108.15</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4682</v>
+        <v>0.4805</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>28.2</v>
+        <v>23.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-22 03:25</t>
+          <t>2026-10-23 03:19</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.85</v>
+        <v>25.4</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.9020999999999999</v>
+        <v>0.8690000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>23.6</v>
+        <v>26.4</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.98</v>
+        <v>39.4</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8365</v>
+        <v>0.8098000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>24.9</v>
+        <v>27.7</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2215</v>
+        <v>0.2387</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>33.4</v>
+        <v>39.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1625</v>
+        <v>1560</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.2218</v>
+        <v>0.1729</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>23.8</v>
+        <v>26.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2420</v>
+        <v>2385</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6631999999999999</v>
+        <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>23.7</v>
+        <v>26.8</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>54</v>
+        <v>52.6</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1415</v>
+        <v>-0.1638</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>24.6</v>
+        <v>27.5</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1842</v>
+        <v>-0.1678</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>31.2</v>
+        <v>39.6</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="F11" s="37" t="n">
-        <v>15.15</v>
+        <v>15.55</v>
       </c>
       <c r="G11" s="43" t="n">
-        <v>-0.3384</v>
+        <v>-0.321</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>30</v>
+        <v>49.7</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>62.1</v>
+        <v>61.9</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>-0.0143</v>
+        <v>-0.0175</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>30</v>
+        <v>33.6</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.35</v>
+        <v>20.5</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>202.5</v>
+        <v>204</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>32.3</v>
+        <v>35.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>28.7</v>
+        <v>34.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>89.8475</v>
+        <v>92.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>33.8</v>
+        <v>36.6</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>30.3</v>
+        <v>29.7</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2387</v>
+        <v>-0.2538</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>27.9</v>
+        <v>29.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3201</v>
+        <v>0.3163</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>28.9</v>
+        <v>33.9</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.1</v>
+        <v>26.05</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1153</v>
+        <v>-0.1169</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>108.15</v>
+        <v>106.9</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4805</v>
+        <v>0.4634</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>23.6</v>
+        <v>28.6</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-23 03:19</t>
+          <t>2026-10-27 04:39</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>0.8690000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>0.8098000000000001</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>27.7</v>
+        <v>28.8</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.2387</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>0.1729</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>0.6392</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>26.8</v>
+        <v>27.9</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>-0.1638</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.1678</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>39.6</v>
+        <v>40.7</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.321</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-0.0175</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>33.6</v>
+        <v>34.7</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>204</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>0.8756999999999999</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>92.55930000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>36.6</v>
+        <v>37.7</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-0.2538</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>29.3</v>
+        <v>30.4</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>0.3163</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-0.1169</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0.4634</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-27 04:39</t>
+          <t>2026-10-28 04:09</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -939,7 +939,7 @@
         <v>0.8690000000000001</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.4</v>
+        <v>39.26</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8098000000000001</v>
+        <v>0.8034</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="F6" s="37" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.2387</v>
+        <v>0.2485</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1560</v>
+        <v>1510</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.1729</v>
+        <v>0.1353</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2385</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6392</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>27.9</v>
+        <v>28.6</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>52.6</v>
+        <v>51.8</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1638</v>
+        <v>-0.1765</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>-0.1678</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>40.7</v>
+        <v>32.4</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.321</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>50.8</v>
+        <v>45.3</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="G12" s="43" t="n">
-        <v>-0.0175</v>
+        <v>63</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>0</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>34.7</v>
+        <v>37.1</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.5</v>
+        <v>20.45</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>204</v>
+        <v>203.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>36.2</v>
+        <v>37.1</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>158.5</v>
+        <v>162</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.8756999999999999</v>
+        <v>0.9172</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>35.1</v>
+        <v>38.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>92.55930000000001</v>
+        <v>92.22030000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2538</v>
+        <v>-0.2412</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>69.5</v>
+        <v>68.5</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.3163</v>
+        <v>0.2973</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>35</v>
+        <v>35.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>26.05</v>
+        <v>25.55</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1169</v>
+        <v>-0.1339</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>32.5</v>
+        <v>31.4</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.9</v>
+        <v>106.6</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4634</v>
+        <v>0.4593</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-28 04:09</t>
+          <t>2026-10-29 04:24</t>
         </is>
       </c>
     </row>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="F4" s="37" t="n">
-        <v>25.4</v>
+        <v>26.07</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.8690000000000001</v>
+        <v>0.9183</v>
       </c>
       <c r="H4" s="39" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F5" s="37" t="n">
-        <v>39.26</v>
+        <v>40.13</v>
       </c>
       <c r="G5" s="38" t="n">
-        <v>0.8034</v>
+        <v>0.8434</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>29.5</v>
+        <v>28</v>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>0.2485</v>
       </c>
       <c r="H6" s="39" t="n">
-        <v>41.1</v>
+        <v>38.3</v>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="F7" s="37" t="n">
-        <v>1510</v>
+        <v>1550</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.1353</v>
+        <v>0.1654</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="I7" s="40" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="F8" s="37" t="n">
-        <v>2400</v>
+        <v>2425</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.6667000000000001</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="I8" s="40" t="inlineStr">
         <is>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="F9" s="37" t="n">
-        <v>51.8</v>
+        <v>55.7</v>
       </c>
       <c r="G9" s="43" t="n">
-        <v>-0.1765</v>
+        <v>-0.1145</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="I9" s="40" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="F10" s="37" t="n">
-        <v>30.5</v>
+        <v>30.25</v>
       </c>
       <c r="G10" s="43" t="n">
-        <v>-0.1678</v>
+        <v>-0.1746</v>
       </c>
       <c r="H10" s="39" t="n">
-        <v>32.4</v>
+        <v>30.2</v>
       </c>
       <c r="I10" s="40" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>-0.321</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>45.3</v>
+        <v>38</v>
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="F12" s="37" t="n">
-        <v>63</v>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>0</v>
+        <v>62.9</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="H12" s="39" t="n">
-        <v>37.1</v>
+        <v>35</v>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>20.45</v>
+        <v>20.25</v>
       </c>
       <c r="G13" s="38" t="n">
-        <v>203.5</v>
+        <v>201.5</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>37.1</v>
+        <v>32.6</v>
       </c>
       <c r="I13" s="40" t="inlineStr">
         <is>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.9172</v>
+        <v>0.9053</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>38.1</v>
+        <v>35.1</v>
       </c>
       <c r="I14" s="40" t="inlineStr">
         <is>
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>55</v>
+        <v>53.9</v>
       </c>
       <c r="G15" s="38" t="n">
-        <v>92.22030000000001</v>
+        <v>90.35590000000001</v>
       </c>
       <c r="H15" s="39" t="n">
-        <v>38.5</v>
+        <v>31.4</v>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>30.2</v>
+        <v>29.75</v>
       </c>
       <c r="G16" s="43" t="n">
-        <v>-0.2412</v>
+        <v>-0.2525</v>
       </c>
       <c r="H16" s="39" t="n">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G17" s="38" t="n">
-        <v>0.2973</v>
+        <v>0.2992</v>
       </c>
       <c r="H17" s="39" t="n">
-        <v>35.6</v>
+        <v>33.6</v>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>25.55</v>
+        <v>25.2</v>
       </c>
       <c r="G19" s="43" t="n">
-        <v>-0.1339</v>
+        <v>-0.1458</v>
       </c>
       <c r="H19" s="39" t="n">
-        <v>31.4</v>
+        <v>26.3</v>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>106.6</v>
+        <v>108.65</v>
       </c>
       <c r="G23" s="38" t="n">
-        <v>0.4593</v>
+        <v>0.4873</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="I23" s="40" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B36" s="44" t="inlineStr">
         <is>
-          <t>2026-10-29 04:24</t>
+          <t>2026-10-30 04:23</t>
         </is>
       </c>
     </row>
